--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_88_R9.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_88_R9.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6826</v>
+        <v>3.3261</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1731</v>
+        <v>4.134</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4905</v>
+        <v>-0.8079</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7299</v>
+        <v>2.1776</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7901</v>
+        <v>-2.4129</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0603</v>
+        <v>4.5906</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4937</v>
+        <v>5.5908</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6716</v>
+        <v>-1.6329</v>
       </c>
       <c r="L2" t="n">
-        <v>3.1652</v>
+        <v>7.2237</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.2235</v>
+        <v>-3.4131</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1186</v>
+        <v>-0.78</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.1049</v>
+        <v>-2.6331</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0154</v>
+        <v>2.0876</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0154</v>
+        <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>0.861</v>
+        <v>-1.4752</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5351</v>
+        <v>-0.8331</v>
       </c>
       <c r="U2" t="n">
-        <v>0.326</v>
+        <v>-0.642</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1444</v>
+        <v>0.5361</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4532</v>
+        <v>2.5523</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6308</v>
+        <v>4.3789</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1775</v>
+        <v>-1.8266</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1776</v>
+        <v>-0.7299</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.4129</v>
+        <v>-0.7901</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5906</v>
+        <v>0.0603</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5908</v>
+        <v>2.4937</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.6329</v>
+        <v>-0.6716</v>
       </c>
       <c r="L3" t="n">
-        <v>7.2237</v>
+        <v>3.1652</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.4131</v>
+        <v>-3.2235</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.78</v>
+        <v>-0.1186</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.6331</v>
+        <v>-3.1049</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0876</v>
+        <v>3.0154</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2473</v>
+        <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.3481</v>
+        <v>-0.2693</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3364</v>
+        <v>-0.2592</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0117</v>
+        <v>-0.0101</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>2.1444</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4025</v>
+        <v>2.4435</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3664</v>
+        <v>2.251</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.9638</v>
+        <v>0.1926</v>
       </c>
       <c r="G4" t="n">
-        <v>3.061</v>
+        <v>0.6272</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9496</v>
+        <v>2.7754</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1113</v>
+        <v>-2.1481</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7264</v>
+        <v>3.1039</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1932</v>
+        <v>2.7259</v>
       </c>
       <c r="L4" t="n">
-        <v>3.5333</v>
+        <v>0.378</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6655</v>
+        <v>-2.4766</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2435</v>
+        <v>0.0495</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.422</v>
+        <v>-2.5261</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>3.0154</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3</v>
+        <v>-1.1991</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4323</v>
+        <v>-0.8529</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1322</v>
+        <v>-0.3462</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0418</v>
+        <v>2.4107</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9836</v>
+        <v>5.6769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0581</v>
+        <v>-3.2663</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6272</v>
+        <v>3.061</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7754</v>
+        <v>0.9496</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1481</v>
+        <v>2.1113</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1039</v>
+        <v>4.7264</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7259</v>
+        <v>1.1932</v>
       </c>
       <c r="L5" t="n">
-        <v>0.378</v>
+        <v>3.5333</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4766</v>
+        <v>-1.6655</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0495</v>
+        <v>-0.2435</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.5261</v>
+        <v>-1.422</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6008</v>
+        <v>-0.2919</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1202</v>
+        <v>-0.1217</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4806</v>
+        <v>-0.1702</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5742</v>
+        <v>1.1953</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9024</v>
+        <v>2.5235</v>
       </c>
       <c r="F6" t="n">
         <v>-1.3282</v>
@@ -922,10 +922,10 @@
         <v>3.4793</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6157</v>
+        <v>-0.9946</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1791</v>
+        <v>-0.5579</v>
       </c>
       <c r="U6" t="n">
         <v>-0.4367</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3004</v>
+        <v>0.2215</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08840000000000001</v>
+        <v>0.2654</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.212</v>
+        <v>-0.044</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5855</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8746</v>
+        <v>-0.3528</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2851</v>
+        <v>-0.1171</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3306</v>
+        <v>-0.4656</v>
       </c>
       <c r="E8" t="n">
-        <v>0.63</v>
+        <v>0.3941</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9606</v>
+        <v>-0.8597</v>
       </c>
       <c r="G8" t="n">
         <v>-0.968</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2904</v>
+        <v>-0.4255</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1968</v>
+        <v>-0.0391</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4872</v>
+        <v>-0.3864</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.434</v>
+        <v>-3.0231</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1643</v>
+        <v>-2.5181</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2697</v>
+        <v>-0.505</v>
       </c>
       <c r="G9" t="n">
         <v>-0.406</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6884</v>
+        <v>0.0993</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4955</v>
+        <v>0.1417</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1929</v>
+        <v>-0.0424</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3247</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3761</v>
+        <v>-3.5561</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8753</v>
+        <v>-2.1873</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5008</v>
+        <v>-1.3689</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2753</v>
+        <v>-2.5331</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0708</v>
+        <v>-2.6603</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2045</v>
+        <v>0.1271</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4455</v>
+        <v>-1.9004</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5559</v>
+        <v>-2.2918</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1104</v>
+        <v>0.3914</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8299</v>
+        <v>-0.6327</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5149</v>
+        <v>-0.3684</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3149</v>
+        <v>-0.2643</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4353</v>
+        <v>-0.4147</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5702</v>
+        <v>-0.2869</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1349</v>
+        <v>-0.1278</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8592</v>
+        <v>-3.6963</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4232</v>
+        <v>-1.2291</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4361</v>
+        <v>-2.4672</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5331</v>
+        <v>-3.2753</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6603</v>
+        <v>-2.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1271</v>
+        <v>-1.2045</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9004</v>
+        <v>-1.4455</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2918</v>
+        <v>-1.5559</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3914</v>
+        <v>0.1104</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6327</v>
+        <v>-1.8299</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3684</v>
+        <v>-0.5149</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2643</v>
+        <v>-1.3149</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7178</v>
+        <v>0.1151</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5228</v>
+        <v>0.2164</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.195</v>
+        <v>-0.1013</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1931</v>
+        <v>-6.0005</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2475</v>
+        <v>-4.0549</v>
       </c>
       <c r="F12" t="n">
         <v>-1.9456</v>
@@ -1390,10 +1390,10 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0772</v>
+        <v>-0.8845</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8215</v>
+        <v>-0.6289</v>
       </c>
       <c r="U12" t="n">
         <v>-0.2557</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3391</v>
+        <v>-4.592200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>8.887599999999999</v>
+        <v>9.634399999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.2267</v>
+        <v>-14.2268</v>
       </c>
       <c r="G13" t="n">
         <v>-4.931799999999999</v>
@@ -1468,16 +1468,16 @@
         <v>19.716</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.8399</v>
+        <v>-6.0932</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.204200000000001</v>
+        <v>-3.4573</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.6358</v>
+        <v>-2.6359</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.0052</v>
+        <v>-4.005199999999999</v>
       </c>
       <c r="W13" t="n">
         <v>4.178100000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.212199999999999</v>
+        <v>9.0937</v>
       </c>
       <c r="E14" t="n">
-        <v>8.717000000000001</v>
+        <v>9.306800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5048</v>
+        <v>-0.2131</v>
       </c>
       <c r="G14" t="n">
         <v>3.3702</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0009</v>
+        <v>0.8806</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4402</v>
+        <v>0.1496</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4393</v>
+        <v>0.731</v>
       </c>
       <c r="V14" t="n">
         <v>4.147</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4632</v>
+        <v>2.4176</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7607</v>
+        <v>4.2889</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2975</v>
+        <v>-1.8713</v>
       </c>
       <c r="G15" t="n">
         <v>3.6673</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3627</v>
+        <v>1.317</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2819</v>
+        <v>0.8101</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0808</v>
+        <v>0.507</v>
       </c>
       <c r="V15" t="n">
         <v>1.6083</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1177</v>
+        <v>1.9823</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7428</v>
+        <v>0.586</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3749</v>
+        <v>1.3963</v>
       </c>
       <c r="G16" t="n">
-        <v>0.771</v>
+        <v>0.7125</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4034</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6323</v>
+        <v>-0.1338</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8788</v>
+        <v>0.7589</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1427</v>
+        <v>0.5749</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7361</v>
+        <v>0.184</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1078</v>
+        <v>-0.0464</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2606</v>
+        <v>0.2714</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3684</v>
+        <v>-0.3178</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7178</v>
+        <v>0.342</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4876</v>
+        <v>-0.1729</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2302</v>
+        <v>0.5149</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3247</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7299</v>
+        <v>1.6967</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4681</v>
+        <v>1.3889</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2618</v>
+        <v>0.3077</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7125</v>
+        <v>0.771</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8463000000000001</v>
+        <v>1.4034</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1338</v>
+        <v>-0.6323</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7589</v>
+        <v>1.8788</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5749</v>
+        <v>1.1427</v>
       </c>
       <c r="L17" t="n">
-        <v>0.184</v>
+        <v>0.7361</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0464</v>
+        <v>-1.1078</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2714</v>
+        <v>0.2606</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3178</v>
+        <v>-1.3684</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0896</v>
+        <v>0.2967</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2908</v>
+        <v>0.1338</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3804</v>
+        <v>0.163</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.3247</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4842</v>
+        <v>1.1805</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6041</v>
+        <v>3.0759</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1199</v>
+        <v>-1.8954</v>
       </c>
       <c r="G18" t="n">
         <v>4.8573</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2855</v>
+        <v>0.4107</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5975</v>
+        <v>-0.1256</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3119</v>
+        <v>0.5364</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3152</v>
+        <v>-0.5543</v>
       </c>
       <c r="E19" t="n">
-        <v>0.305</v>
+        <v>0.5831</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0103</v>
+        <v>-1.1373</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4194</v>
+        <v>-0.9949</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0276</v>
+        <v>0.2029</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3918</v>
+        <v>-1.1979</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.132</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4265</v>
+        <v>0.1211</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2944</v>
+        <v>0.5386</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2874</v>
+        <v>-1.6547</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6012</v>
+        <v>0.0818</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6862</v>
+        <v>-1.7365</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.6237</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>3.897</v>
+        <v>0.224</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9189</v>
+        <v>0.0984</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9782</v>
+        <v>0.1256</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9304</v>
+        <v>1.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8194</v>
+        <v>-0.9367</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7794</v>
+        <v>-0.1733</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5988</v>
+        <v>-0.7635</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4671</v>
+        <v>-0.8935</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1091</v>
+        <v>-0.1608</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.358</v>
+        <v>-0.7327</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6731</v>
+        <v>0.1608</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1344</v>
+        <v>0.0504</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5386</v>
+        <v>0.1104</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1401</v>
+        <v>-1.0543</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2435</v>
+        <v>-0.2112</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8966</v>
+        <v>-0.8431</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7921</v>
+        <v>0.4206</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3383</v>
+        <v>0.1298</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4538</v>
+        <v>0.2908</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3178</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1112</v>
+        <v>0.6614</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.429</v>
+        <v>-1.6096</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9949</v>
+        <v>-0.4671</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2029</v>
+        <v>-0.1091</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1979</v>
+        <v>-0.358</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6731</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1211</v>
+        <v>0.1344</v>
       </c>
       <c r="L21" t="n">
         <v>0.5386</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6547</v>
+        <v>-1.1401</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0818</v>
+        <v>-0.2435</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7365</v>
+        <v>-0.8966</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5395</v>
+        <v>0.6633</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3734</v>
+        <v>0.2203</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1661</v>
+        <v>0.443</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6083</v>
+        <v>-1.6083</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4479</v>
+        <v>-1.2948</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5271</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9207</v>
+        <v>-0.5382</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8935</v>
+        <v>-2.4194</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1608</v>
+        <v>-1.0276</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7327</v>
+        <v>-1.3918</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1608</v>
+        <v>-0.132</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0504</v>
+        <v>-0.4265</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1104</v>
+        <v>0.2944</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0543</v>
+        <v>-2.2874</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2112</v>
+        <v>-0.6012</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8431</v>
+        <v>-1.6862</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0905</v>
+        <v>2.287</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.224</v>
+        <v>0.8573</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1336</v>
+        <v>1.4297</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7267</v>
+        <v>-1.3342</v>
       </c>
       <c r="E23" t="n">
         <v>-0.6047</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.122</v>
+        <v>-0.7295</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0383</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0075</v>
+        <v>0.4</v>
       </c>
       <c r="T23" t="n">
         <v>0.2636</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2561</v>
+        <v>0.1364</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8759</v>
+        <v>-1.5335</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2909</v>
+        <v>-0.1729</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5851</v>
+        <v>-1.3606</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1527</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4191</v>
+        <v>-0.0767</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2697</v>
+        <v>-0.0452</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7957</v>
+        <v>-2.8572</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7667</v>
+        <v>-2.8846</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0291</v>
+        <v>0.0274</v>
       </c>
       <c r="G25" t="n">
         <v>-2.4807</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3087</v>
+        <v>1.2472</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4208</v>
+        <v>0.3029</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8878</v>
+        <v>0.9443</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5.339</v>
+        <v>6.912000000000001</v>
       </c>
       <c r="E26" t="n">
         <v>15.2989</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.959899999999999</v>
+        <v>-8.3871</v>
       </c>
       <c r="G26" t="n">
         <v>4.931700000000001</v>
@@ -2458,7 +2458,7 @@
         <v>23.1235</v>
       </c>
       <c r="K26" t="n">
-        <v>4.169399999999999</v>
+        <v>4.1694</v>
       </c>
       <c r="L26" t="n">
         <v>18.9537</v>
@@ -2479,16 +2479,16 @@
         <v>-19.716</v>
       </c>
       <c r="R26" t="n">
-        <v>9.2782</v>
+        <v>9.278200000000002</v>
       </c>
       <c r="S26" t="n">
-        <v>6.839900000000001</v>
+        <v>8.4124</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6358</v>
+        <v>2.6359</v>
       </c>
       <c r="U26" t="n">
-        <v>4.2041</v>
+        <v>5.7769</v>
       </c>
       <c r="V26" t="n">
         <v>4.0052</v>
